--- a/TuVung.xlsx
+++ b/TuVung.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Duy-PC\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git-Soft\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Accommodation</t>
   </si>
@@ -120,6 +120,54 @@
   </si>
   <si>
     <t>Many students choose to live in a dormitory during their first year.</t>
+  </si>
+  <si>
+    <t>Roommate</t>
+  </si>
+  <si>
+    <t>/ˈruːmmeɪt/</t>
+  </si>
+  <si>
+    <t>Bạn cùng phòng</t>
+  </si>
+  <si>
+    <t>My roommate is very friendly and helpful.</t>
+  </si>
+  <si>
+    <t>Furnished</t>
+  </si>
+  <si>
+    <t>/ˈfɜːrnɪʃt/</t>
+  </si>
+  <si>
+    <t>Đầy đủ nội thất</t>
+  </si>
+  <si>
+    <t>The apartment is fully furnished and ready to move into.</t>
+  </si>
+  <si>
+    <t>Unfurnished</t>
+  </si>
+  <si>
+    <t>/ʌnˈfɜːrnɪʃt/</t>
+  </si>
+  <si>
+    <t>Không có nội thất</t>
+  </si>
+  <si>
+    <t>The apartment is unfurnished, so you'll need to buy furniture.</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>/juːˈtɪlətiz/</t>
+  </si>
+  <si>
+    <t>Các chi phí điện, nước, internet, gas</t>
+  </si>
+  <si>
+    <t>Utilities are included in the monthly rent.</t>
   </si>
 </sst>
 </file>
@@ -163,12 +211,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,12 +498,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E9"/>
+  <dimension ref="B2:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -570,6 +620,62 @@
         <v>31</v>
       </c>
     </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/TuVung.xlsx
+++ b/TuVung.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>Accommodation</t>
   </si>
@@ -168,13 +168,244 @@
   </si>
   <si>
     <t>Utilities are included in the monthly rent.</t>
+  </si>
+  <si>
+    <t>Move in</t>
+  </si>
+  <si>
+    <t>/muːv ɪn/</t>
+  </si>
+  <si>
+    <t>Chuyển đến ở</t>
+  </si>
+  <si>
+    <t>She moved into her new apartment last month.</t>
+  </si>
+  <si>
+    <t>Move out</t>
+  </si>
+  <si>
+    <t>Chuyển đi khỏi nơi ở</t>
+  </si>
+  <si>
+    <t>/muːv aʊt/</t>
+  </si>
+  <si>
+    <t>The tenants must move out by the end of June.</t>
+  </si>
+  <si>
+    <t>Vacancy</t>
+  </si>
+  <si>
+    <t>/ˈveɪkənsi/</t>
+  </si>
+  <si>
+    <t>Phòng trống</t>
+  </si>
+  <si>
+    <t>Is there any vacancy in this apartment building?</t>
+  </si>
+  <si>
+    <t>Reservation</t>
+  </si>
+  <si>
+    <t>/ˌrezərˈveɪʃən/</t>
+  </si>
+  <si>
+    <t>Đặt chỗ</t>
+  </si>
+  <si>
+    <t>I made a reservation for a hotel room online.</t>
+  </si>
+  <si>
+    <t>Hostel</t>
+  </si>
+  <si>
+    <t>/ˈhɒstl/</t>
+  </si>
+  <si>
+    <t>Nhà nghỉ giá rẻ</t>
+  </si>
+  <si>
+    <t>Backpackers often stay in hostels to save money.</t>
+  </si>
+  <si>
+    <t>Neighborhood</t>
+  </si>
+  <si>
+    <t>/ˈneɪbərhʊd/</t>
+  </si>
+  <si>
+    <t>Khu dân cư</t>
+  </si>
+  <si>
+    <t>The neighborhood is safe and convenient.</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>/həʊˈtel/</t>
+  </si>
+  <si>
+    <t>Khách sạn</t>
+  </si>
+  <si>
+    <t>We stayed at a hotel near the beach.</t>
+  </si>
+  <si>
+    <t>Đoạn hội thoại thực tế khi tìm thuê nhà</t>
+  </si>
+  <si>
+    <r>
+      <t>A:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Are you looking for accommodation near the university?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Yes, I'm searching for a furnished apartment.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> What's your budget for rent?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Around $600 per month, including utilities.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> There is a vacancy in my building. The landlord is looking for a new tenant.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Great! Do I need to pay a deposit?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Yes, one month's rent as a security deposit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> That sounds reasonable. Can I schedule a visit before signing the lease?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Of course. You can come this weekend.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +419,15 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -211,13 +451,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E13"/>
+  <dimension ref="B2:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -508,7 +752,7 @@
     <col min="10" max="10" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,8 +765,11 @@
       <c r="E2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -536,7 +783,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>8</v>
       </c>
@@ -549,8 +796,11 @@
       <c r="E4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -563,8 +813,11 @@
       <c r="E5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -577,8 +830,11 @@
       <c r="E6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>20</v>
       </c>
@@ -591,8 +847,11 @@
       <c r="E7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>24</v>
       </c>
@@ -605,8 +864,11 @@
       <c r="E8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>30</v>
       </c>
@@ -619,8 +881,11 @@
       <c r="E9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>32</v>
       </c>
@@ -633,8 +898,11 @@
       <c r="E10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>36</v>
       </c>
@@ -647,8 +915,11 @@
       <c r="E11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>40</v>
       </c>
@@ -661,8 +932,11 @@
       <c r="E12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>44</v>
       </c>
@@ -674,6 +948,104 @@
       </c>
       <c r="E13" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
